--- a/data/rebotes.xlsx
+++ b/data/rebotes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hector.andagua\Downloads\Entel\REBOTES\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2C318B-7EEC-4FE1-9539-7773F6162890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782D0555-F2D5-4592-8AA7-88A1F79F1992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EC36A456-6C51-485E-8767-0E06DC2B8372}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$M$1694</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$M$1841</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20329" uniqueCount="1569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22093" uniqueCount="1653">
   <si>
     <t>DOCUMENTO</t>
   </si>
@@ -4746,6 +4746,258 @@
   </si>
   <si>
     <t>73465848</t>
+  </si>
+  <si>
+    <t>INC_PP 24May_9 a 12pm</t>
+  </si>
+  <si>
+    <t>INC_PP 23May_3 a 9pm</t>
+  </si>
+  <si>
+    <t>INC_PP 25May_9 a 12pm</t>
+  </si>
+  <si>
+    <t>INC_PP 24May_12 a 3pm</t>
+  </si>
+  <si>
+    <t>INC_PP 23May_12 a 3pm</t>
+  </si>
+  <si>
+    <t>INC_PP 23May_9 a 12pm</t>
+  </si>
+  <si>
+    <t>INC_PP 22May_3 a 9pm</t>
+  </si>
+  <si>
+    <t>INC_PP 24May_3 a 9pm</t>
+  </si>
+  <si>
+    <t>19226610</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 19226610 no existe</t>
+  </si>
+  <si>
+    <t>60085104</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 60085104 no existe</t>
+  </si>
+  <si>
+    <t>46050267</t>
+  </si>
+  <si>
+    <t>47881314</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 47881314 no existe</t>
+  </si>
+  <si>
+    <t>75462367</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 75462367 no existe</t>
+  </si>
+  <si>
+    <t>60658624</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 60658624 no existe</t>
+  </si>
+  <si>
+    <t>60484184</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 60484184 no existe</t>
+  </si>
+  <si>
+    <t>74761980</t>
+  </si>
+  <si>
+    <t>60135818</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 60135818 no existe</t>
+  </si>
+  <si>
+    <t>20113275</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 20113275 no existe</t>
+  </si>
+  <si>
+    <t>45506812</t>
+  </si>
+  <si>
+    <t>INC_OSS Captura N7 23May</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 45506812 no existe</t>
+  </si>
+  <si>
+    <t>60212435</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 60212435 no existe</t>
+  </si>
+  <si>
+    <t>71048659</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 71048659 no existe</t>
+  </si>
+  <si>
+    <t>73429020</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 73429020 no existe</t>
+  </si>
+  <si>
+    <t>73117901</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 73117901 no existe</t>
+  </si>
+  <si>
+    <t>43570095</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 43570095 no existe</t>
+  </si>
+  <si>
+    <t>73431753</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 73431753 no existe</t>
+  </si>
+  <si>
+    <t>007388556</t>
+  </si>
+  <si>
+    <t>74468135</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 74468135 no existe</t>
+  </si>
+  <si>
+    <t>76556659</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 76556659 no existe</t>
+  </si>
+  <si>
+    <t>75832412</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 75832412 no existe</t>
+  </si>
+  <si>
+    <t>60295706</t>
+  </si>
+  <si>
+    <t>INC_OSS Captura N7 22May</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 60295706 no existe</t>
+  </si>
+  <si>
+    <t>71800159</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 71800159 no existe</t>
+  </si>
+  <si>
+    <t>09508321</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 09508321 no existe</t>
+  </si>
+  <si>
+    <t>60494639</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 60494639 no existe</t>
+  </si>
+  <si>
+    <t>75207595</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 75207595 no existe</t>
+  </si>
+  <si>
+    <t>43696215</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 43696215 no existe</t>
+  </si>
+  <si>
+    <t>72412707</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 72412707 no existe</t>
+  </si>
+  <si>
+    <t>44123031</t>
+  </si>
+  <si>
+    <t>21014131</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 21014131 no existe</t>
+  </si>
+  <si>
+    <t>INC_OSS Captura N7 21May</t>
+  </si>
+  <si>
+    <t>42406923</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 42406923 no existe</t>
+  </si>
+  <si>
+    <t>76979701</t>
+  </si>
+  <si>
+    <t>INC_PP 25May_12 a 3pm</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 76979701 no existe</t>
+  </si>
+  <si>
+    <t>75100378</t>
+  </si>
+  <si>
+    <t>INC_PP 25May_3 a 9pm</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 75100378 no existe</t>
+  </si>
+  <si>
+    <t>INC_PP 26May_9 a 12pm</t>
+  </si>
+  <si>
+    <t>02064398</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 02064398 no existe</t>
+  </si>
+  <si>
+    <t>73580011</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 73580011 no existe</t>
+  </si>
+  <si>
+    <t>76403481</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 76403481 no existe</t>
+  </si>
+  <si>
+    <t>70715052</t>
+  </si>
+  <si>
+    <t>El beneficiario con documento 70715052 no existe</t>
   </si>
 </sst>
 </file>
@@ -4851,22 +5103,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{D3869D4D-DBED-4A46-ADD9-94133D70DF9A}"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color theme="0" tint="-0.24994659260841701"/>
@@ -74668,1180 +74905,6031 @@
       </c>
     </row>
     <row r="1695" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1695" s="3"/>
-      <c r="C1695" s="4"/>
-      <c r="F1695" s="5"/>
-      <c r="G1695" s="5"/>
-      <c r="L1695" s="5"/>
-      <c r="M1695" s="6"/>
+      <c r="A1695" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="B1695" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1695" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1695" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1695" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="F1695" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1695" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1695" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="I1695" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1695" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1695" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1695" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1695" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1696" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1696" s="3"/>
-      <c r="C1696" s="4"/>
-      <c r="F1696" s="5"/>
-      <c r="G1696" s="5"/>
-      <c r="L1696" s="5"/>
-      <c r="M1696" s="6"/>
+      <c r="A1696" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="B1696" s="6" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C1696" s="8">
+        <v>48</v>
+      </c>
+      <c r="D1696" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1696" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1696" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1696" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1696" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="I1696" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1696" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1696" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1696" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1696" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1697" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1697" s="3"/>
-      <c r="C1697" s="4"/>
-      <c r="F1697" s="5"/>
-      <c r="G1697" s="5"/>
-      <c r="L1697" s="5"/>
-      <c r="M1697" s="6"/>
+      <c r="A1697" s="6" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B1697" s="6" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C1697" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1697" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1697" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1697" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1697" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1697" s="6" t="s">
+        <v>1395</v>
+      </c>
+      <c r="I1697" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1697" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1697" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1697" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1697" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1698" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1698" s="3"/>
-      <c r="C1698" s="4"/>
-      <c r="F1698" s="5"/>
-      <c r="G1698" s="5"/>
-      <c r="L1698" s="5"/>
-      <c r="M1698" s="6"/>
+      <c r="A1698" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B1698" s="6" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C1698" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1698" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1698" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1698" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1698" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1698" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1698" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1698" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1698" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1698" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1698" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1699" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1699" s="3"/>
-      <c r="C1699" s="4"/>
-      <c r="F1699" s="5"/>
-      <c r="G1699" s="5"/>
-      <c r="L1699" s="5"/>
-      <c r="M1699" s="6"/>
+      <c r="A1699" s="6" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B1699" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1699" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1699" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1699" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1699" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1699" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1699" s="6" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I1699" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1699" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1699" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1699" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1699" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1700" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1700" s="3"/>
-      <c r="C1700" s="4"/>
-      <c r="F1700" s="5"/>
-      <c r="G1700" s="5"/>
-      <c r="L1700" s="5"/>
-      <c r="M1700" s="6"/>
+      <c r="A1700" s="6" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B1700" s="6" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C1700" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1700" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1700" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1700" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1700" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1700" s="6" t="s">
+        <v>1559</v>
+      </c>
+      <c r="I1700" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1700" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1700" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1700" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1700" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1701" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1701" s="3"/>
-      <c r="C1701" s="4"/>
-      <c r="F1701" s="5"/>
-      <c r="G1701" s="5"/>
-      <c r="L1701" s="5"/>
-      <c r="M1701" s="6"/>
+      <c r="A1701" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B1701" s="6" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C1701" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1701" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1701" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1701" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1701" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1701" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1701" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1701" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1701" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1701" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1701" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1702" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1702" s="3"/>
-      <c r="C1702" s="4"/>
-      <c r="F1702" s="5"/>
-      <c r="G1702" s="5"/>
-      <c r="L1702" s="5"/>
-      <c r="M1702" s="6"/>
+      <c r="A1702" s="6" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B1702" s="6" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C1702" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1702" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1702" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1702" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1702" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1702" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1702" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1702" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1702" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1702" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1702" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1703" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1703" s="3"/>
-      <c r="C1703" s="4"/>
-      <c r="F1703" s="5"/>
-      <c r="G1703" s="5"/>
-      <c r="L1703" s="5"/>
-      <c r="M1703" s="6"/>
+      <c r="A1703" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="B1703" s="6" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C1703" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1703" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1703" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1703" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1703" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1703" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="I1703" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1703" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1703" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1703" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1703" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1704" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1704" s="3"/>
-      <c r="C1704" s="4"/>
-      <c r="F1704" s="5"/>
-      <c r="G1704" s="5"/>
-      <c r="L1704" s="5"/>
-      <c r="M1704" s="6"/>
+      <c r="A1704" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1704" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1704" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1704" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1704" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1704" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1704" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1704" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="I1704" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1704" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1704" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1704" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1704" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1705" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1705" s="3"/>
-      <c r="C1705" s="4"/>
-      <c r="F1705" s="5"/>
-      <c r="G1705" s="5"/>
-      <c r="L1705" s="5"/>
-      <c r="M1705" s="6"/>
+      <c r="A1705" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1705" s="6" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C1705" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1705" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1705" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1705" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1705" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1705" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="I1705" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1705" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1705" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1705" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1705" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1706" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1706" s="3"/>
-      <c r="C1706" s="4"/>
-      <c r="F1706" s="5"/>
-      <c r="G1706" s="5"/>
-      <c r="L1706" s="5"/>
-      <c r="M1706" s="6"/>
+      <c r="A1706" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="B1706" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1706" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1706" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1706" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1706" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1706" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1706" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="I1706" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1706" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1706" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1706" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1706" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1707" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1707" s="3"/>
-      <c r="C1707" s="4"/>
-      <c r="F1707" s="5"/>
-      <c r="G1707" s="5"/>
-      <c r="L1707" s="5"/>
-      <c r="M1707" s="6"/>
+      <c r="A1707" s="6" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B1707" s="6" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C1707" s="8">
+        <v>21</v>
+      </c>
+      <c r="D1707" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1707" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1707" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1707" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1707" s="6" t="s">
+        <v>1578</v>
+      </c>
+      <c r="I1707" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1707" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1707" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1707" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1707" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1708" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1708" s="3"/>
-      <c r="C1708" s="4"/>
-      <c r="F1708" s="5"/>
-      <c r="G1708" s="5"/>
-      <c r="L1708" s="5"/>
-      <c r="M1708" s="6"/>
+      <c r="A1708" s="6" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B1708" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1708" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1708" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1708" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1708" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1708" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1708" s="6" t="s">
+        <v>1580</v>
+      </c>
+      <c r="I1708" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1708" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1708" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1708" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1708" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1709" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1709" s="3"/>
-      <c r="C1709" s="4"/>
-      <c r="F1709" s="5"/>
-      <c r="G1709" s="5"/>
-      <c r="L1709" s="5"/>
-      <c r="M1709" s="6"/>
+      <c r="A1709" s="6" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B1709" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1709" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1709" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1709" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1709" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1709" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1709" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1709" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1709" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1709" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1709" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1709" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1710" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1710" s="3"/>
-      <c r="C1710" s="4"/>
-      <c r="F1710" s="5"/>
-      <c r="G1710" s="5"/>
-      <c r="L1710" s="5"/>
-      <c r="M1710" s="6"/>
+      <c r="A1710" s="6" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B1710" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1710" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1710" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1710" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1710" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1710" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1710" s="6" t="s">
+        <v>1583</v>
+      </c>
+      <c r="I1710" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1710" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1710" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1710" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1710" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1711" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1711" s="3"/>
-      <c r="C1711" s="4"/>
-      <c r="F1711" s="5"/>
-      <c r="G1711" s="5"/>
-      <c r="L1711" s="5"/>
-      <c r="M1711" s="6"/>
+      <c r="A1711" s="6" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B1711" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1711" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1711" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1711" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1711" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1711" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1711" s="6" t="s">
+        <v>1585</v>
+      </c>
+      <c r="I1711" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1711" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1711" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1711" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1711" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1712" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1712" s="3"/>
-      <c r="C1712" s="4"/>
-      <c r="F1712" s="5"/>
-      <c r="G1712" s="5"/>
-      <c r="L1712" s="5"/>
-      <c r="M1712" s="6"/>
+      <c r="A1712" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="B1712" s="6" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C1712" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1712" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1712" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1712" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1712" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1712" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="I1712" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1712" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1712" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1712" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1712" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1713" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1713" s="3"/>
-      <c r="C1713" s="4"/>
-      <c r="F1713" s="5"/>
-      <c r="G1713" s="5"/>
-      <c r="L1713" s="5"/>
-      <c r="M1713" s="6"/>
+      <c r="A1713" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B1713" s="6" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C1713" s="8">
+        <v>49</v>
+      </c>
+      <c r="D1713" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1713" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1713" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1713" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1713" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1713" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1713" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1713" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1713" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1713" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1714" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1714" s="3"/>
-      <c r="C1714" s="4"/>
-      <c r="F1714" s="5"/>
-      <c r="G1714" s="5"/>
-      <c r="L1714" s="5"/>
-      <c r="M1714" s="6"/>
+      <c r="A1714" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="B1714" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1714" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1714" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1714" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1714" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1714" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1714" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="I1714" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1714" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1714" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1714" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1714" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1715" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1715" s="3"/>
-      <c r="C1715" s="4"/>
-      <c r="F1715" s="5"/>
-      <c r="G1715" s="5"/>
-      <c r="L1715" s="5"/>
-      <c r="M1715" s="6"/>
+      <c r="A1715" s="6" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1715" s="6" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C1715" s="8">
+        <v>35</v>
+      </c>
+      <c r="D1715" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1715" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1715" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1715" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1715" s="6" t="s">
+        <v>1587</v>
+      </c>
+      <c r="I1715" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1715" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1715" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1715" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1715" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1716" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1716" s="3"/>
-      <c r="C1716" s="4"/>
-      <c r="F1716" s="5"/>
-      <c r="G1716" s="5"/>
-      <c r="L1716" s="5"/>
-      <c r="M1716" s="6"/>
+      <c r="A1716" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B1716" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1716" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1716" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1716" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1716" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1716" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1716" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1716" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1716" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1716" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1716" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1716" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1717" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1717" s="3"/>
-      <c r="C1717" s="4"/>
-      <c r="F1717" s="5"/>
-      <c r="G1717" s="5"/>
-      <c r="L1717" s="5"/>
-      <c r="M1717" s="6"/>
+      <c r="A1717" s="6" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B1717" s="6" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C1717" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1717" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1717" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1717" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1717" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1717" s="6" t="s">
+        <v>1567</v>
+      </c>
+      <c r="I1717" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1717" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1717" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1717" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1717" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1718" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1718" s="3"/>
-      <c r="C1718" s="4"/>
-      <c r="F1718" s="5"/>
-      <c r="G1718" s="5"/>
-      <c r="L1718" s="5"/>
-      <c r="M1718" s="6"/>
+      <c r="A1718" s="6" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B1718" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1718" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1718" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1718" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1718" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1718" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1718" s="6" t="s">
+        <v>1589</v>
+      </c>
+      <c r="I1718" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1718" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1718" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1718" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1718" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1719" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1719" s="3"/>
-      <c r="C1719" s="4"/>
-      <c r="F1719" s="5"/>
-      <c r="G1719" s="5"/>
-      <c r="L1719" s="5"/>
-      <c r="M1719" s="6"/>
+      <c r="A1719" s="6" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B1719" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1719" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1719" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1719" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1719" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1719" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1719" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1719" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1719" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1719" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1719" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1719" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1720" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1720" s="3"/>
-      <c r="C1720" s="4"/>
-      <c r="F1720" s="5"/>
-      <c r="G1720" s="5"/>
-      <c r="L1720" s="5"/>
-      <c r="M1720" s="6"/>
+      <c r="A1720" s="6" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B1720" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1720" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1720" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1720" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1720" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1720" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1720" s="6" t="s">
+        <v>1578</v>
+      </c>
+      <c r="I1720" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1720" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1720" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1720" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1720" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1721" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1721" s="3"/>
-      <c r="C1721" s="4"/>
-      <c r="F1721" s="5"/>
-      <c r="G1721" s="5"/>
-      <c r="L1721" s="5"/>
-      <c r="M1721" s="6"/>
+      <c r="A1721" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1721" s="6" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C1721" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1721" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1721" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1721" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1721" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1721" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="I1721" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1721" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1721" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1721" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1721" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1722" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1722" s="3"/>
-      <c r="C1722" s="4"/>
-      <c r="F1722" s="5"/>
-      <c r="G1722" s="5"/>
-      <c r="L1722" s="5"/>
-      <c r="M1722" s="6"/>
+      <c r="A1722" s="6" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B1722" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1722" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1722" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1722" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1722" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1722" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1722" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1722" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1722" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1722" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1722" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1722" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1723" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1723" s="3"/>
-      <c r="C1723" s="4"/>
-      <c r="F1723" s="5"/>
-      <c r="G1723" s="5"/>
-      <c r="L1723" s="5"/>
-      <c r="M1723" s="6"/>
+      <c r="A1723" s="6" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B1723" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1723" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1723" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1723" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1723" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1723" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1723" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1723" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1723" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1723" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1723" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1723" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1724" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1724" s="3"/>
-      <c r="C1724" s="4"/>
-      <c r="F1724" s="5"/>
-      <c r="G1724" s="5"/>
-      <c r="L1724" s="5"/>
-      <c r="M1724" s="6"/>
+      <c r="A1724" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B1724" s="6" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C1724" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1724" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1724" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1724" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1724" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1724" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1724" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1724" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1724" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1724" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1724" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1725" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1725" s="3"/>
-      <c r="C1725" s="4"/>
-      <c r="F1725" s="5"/>
-      <c r="G1725" s="5"/>
-      <c r="L1725" s="5"/>
-      <c r="M1725" s="6"/>
+      <c r="A1725" s="6" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B1725" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1725" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1725" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1725" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1725" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1725" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1725" s="6" t="s">
+        <v>1592</v>
+      </c>
+      <c r="I1725" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1725" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1725" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1725" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1725" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1726" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1726" s="3"/>
-      <c r="C1726" s="4"/>
-      <c r="F1726" s="5"/>
-      <c r="G1726" s="5"/>
-      <c r="L1726" s="5"/>
-      <c r="M1726" s="6"/>
+      <c r="A1726" s="6" t="s">
+        <v>963</v>
+      </c>
+      <c r="B1726" s="6" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C1726" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1726" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1726" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1726" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1726" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1726" s="6" t="s">
+        <v>965</v>
+      </c>
+      <c r="I1726" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1726" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1726" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1726" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1726" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1727" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1727" s="3"/>
-      <c r="C1727" s="4"/>
-      <c r="F1727" s="5"/>
-      <c r="G1727" s="5"/>
-      <c r="L1727" s="5"/>
-      <c r="M1727" s="6"/>
+      <c r="A1727" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="B1727" s="6" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C1727" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1727" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1727" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1727" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1727" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1727" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="I1727" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1727" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1727" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1727" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1727" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1728" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1728" s="3"/>
-      <c r="C1728" s="4"/>
-      <c r="F1728" s="5"/>
-      <c r="G1728" s="5"/>
-      <c r="L1728" s="5"/>
-      <c r="M1728" s="6"/>
+      <c r="A1728" s="6" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B1728" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1728" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1728" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1728" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1728" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1728" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1728" s="6" t="s">
+        <v>1431</v>
+      </c>
+      <c r="I1728" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1728" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1728" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1728" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1728" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1729" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1729" s="3"/>
-      <c r="C1729" s="4"/>
-      <c r="F1729" s="5"/>
-      <c r="G1729" s="5"/>
-      <c r="L1729" s="5"/>
-      <c r="M1729" s="6"/>
+      <c r="A1729" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1729" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1729" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1729" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1729" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1729" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1729" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1729" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1729" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1729" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1729" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1729" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1729" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1730" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1730" s="3"/>
-      <c r="C1730" s="4"/>
-      <c r="F1730" s="5"/>
-      <c r="G1730" s="5"/>
-      <c r="L1730" s="5"/>
-      <c r="M1730" s="6"/>
+      <c r="A1730" s="6" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B1730" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1730" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1730" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1730" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1730" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1730" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1730" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1730" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1730" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1730" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1730" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1730" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1731" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1731" s="3"/>
-      <c r="C1731" s="4"/>
-      <c r="F1731" s="5"/>
-      <c r="G1731" s="5"/>
-      <c r="L1731" s="5"/>
-      <c r="M1731" s="6"/>
+      <c r="A1731" s="6" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B1731" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1731" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1731" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1731" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1731" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1731" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1731" s="6" t="s">
+        <v>1578</v>
+      </c>
+      <c r="I1731" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1731" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1731" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1731" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1731" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1732" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1732" s="3"/>
-      <c r="C1732" s="4"/>
-      <c r="F1732" s="5"/>
-      <c r="G1732" s="5"/>
-      <c r="L1732" s="5"/>
-      <c r="M1732" s="6"/>
+      <c r="A1732" s="6" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B1732" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1732" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1732" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1732" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1732" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1732" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1732" s="6" t="s">
+        <v>1594</v>
+      </c>
+      <c r="I1732" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1732" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1732" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1732" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1732" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1733" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1733" s="3"/>
-      <c r="C1733" s="4"/>
-      <c r="F1733" s="5"/>
-      <c r="G1733" s="5"/>
-      <c r="L1733" s="5"/>
-      <c r="M1733" s="6"/>
+      <c r="A1733" s="6" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B1733" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1733" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1733" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1733" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1733" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1733" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1733" s="6" t="s">
+        <v>1578</v>
+      </c>
+      <c r="I1733" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1733" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1733" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1733" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1733" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1734" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1734" s="3"/>
-      <c r="C1734" s="4"/>
-      <c r="F1734" s="5"/>
-      <c r="G1734" s="5"/>
-      <c r="L1734" s="5"/>
-      <c r="M1734" s="6"/>
+      <c r="A1734" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B1734" s="6" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C1734" s="8">
+        <v>49</v>
+      </c>
+      <c r="D1734" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1734" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1734" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1734" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1734" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1734" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1734" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1734" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1734" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1734" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1735" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1735" s="3"/>
-      <c r="C1735" s="4"/>
-      <c r="F1735" s="5"/>
-      <c r="G1735" s="5"/>
-      <c r="L1735" s="5"/>
-      <c r="M1735" s="6"/>
+      <c r="A1735" s="6" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B1735" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1735" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1735" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1735" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1735" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1735" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1735" s="6" t="s">
+        <v>1538</v>
+      </c>
+      <c r="I1735" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1735" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1735" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1735" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1735" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1736" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1736" s="3"/>
-      <c r="C1736" s="4"/>
-      <c r="F1736" s="5"/>
-      <c r="G1736" s="5"/>
-      <c r="L1736" s="5"/>
-      <c r="M1736" s="6"/>
+      <c r="A1736" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B1736" s="6" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C1736" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1736" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1736" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1736" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1736" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1736" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1736" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1736" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1736" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1736" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1736" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1737" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1737" s="3"/>
-      <c r="C1737" s="4"/>
-      <c r="F1737" s="5"/>
-      <c r="G1737" s="5"/>
-      <c r="L1737" s="5"/>
-      <c r="M1737" s="6"/>
+      <c r="A1737" s="6" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B1737" s="6" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C1737" s="8">
+        <v>20</v>
+      </c>
+      <c r="D1737" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1737" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1737" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1737" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1737" s="6" t="s">
+        <v>1597</v>
+      </c>
+      <c r="I1737" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1737" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1737" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1737" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1737" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1738" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1738" s="3"/>
-      <c r="C1738" s="4"/>
-      <c r="F1738" s="5"/>
-      <c r="G1738" s="5"/>
-      <c r="L1738" s="5"/>
-      <c r="M1738" s="6"/>
+      <c r="A1738" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1738" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1738" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1738" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1738" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1738" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1738" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1738" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1738" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1738" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1738" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1738" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1738" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1739" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1739" s="3"/>
-      <c r="C1739" s="4"/>
-      <c r="F1739" s="5"/>
-      <c r="G1739" s="5"/>
-      <c r="L1739" s="5"/>
-      <c r="M1739" s="6"/>
+      <c r="A1739" s="6" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B1739" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1739" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1739" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1739" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1739" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1739" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1739" s="6" t="s">
+        <v>1599</v>
+      </c>
+      <c r="I1739" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1739" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1739" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1739" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1739" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1740" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1740" s="3"/>
-      <c r="C1740" s="4"/>
-      <c r="F1740" s="5"/>
-      <c r="G1740" s="5"/>
-      <c r="L1740" s="5"/>
-      <c r="M1740" s="6"/>
+      <c r="A1740" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B1740" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1740" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1740" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1740" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1740" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1740" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1740" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1740" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1740" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1740" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1740" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1740" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1741" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1741" s="3"/>
-      <c r="C1741" s="4"/>
-      <c r="F1741" s="5"/>
-      <c r="G1741" s="5"/>
-      <c r="L1741" s="5"/>
-      <c r="M1741" s="6"/>
+      <c r="A1741" s="6" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B1741" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1741" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1741" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1741" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1741" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1741" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1741" s="6" t="s">
+        <v>1601</v>
+      </c>
+      <c r="I1741" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1741" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1741" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1741" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1741" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1742" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1742" s="3"/>
-      <c r="C1742" s="4"/>
-      <c r="F1742" s="5"/>
-      <c r="G1742" s="5"/>
-      <c r="L1742" s="5"/>
-      <c r="M1742" s="6"/>
+      <c r="A1742" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B1742" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1742" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1742" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1742" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1742" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1742" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1742" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1742" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1742" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1742" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1742" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1742" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1743" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1743" s="3"/>
-      <c r="C1743" s="4"/>
-      <c r="F1743" s="5"/>
-      <c r="G1743" s="5"/>
-      <c r="L1743" s="5"/>
-      <c r="M1743" s="6"/>
+      <c r="A1743" s="6" t="s">
+        <v>999</v>
+      </c>
+      <c r="B1743" s="6" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C1743" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1743" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1743" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1743" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1743" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1743" s="6" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I1743" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1743" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1743" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1743" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1743" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1744" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1744" s="3"/>
-      <c r="C1744" s="4"/>
-      <c r="F1744" s="5"/>
-      <c r="G1744" s="5"/>
-      <c r="L1744" s="5"/>
-      <c r="M1744" s="6"/>
+      <c r="A1744" s="6" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B1744" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1744" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1744" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1744" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1744" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1744" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1744" s="6" t="s">
+        <v>1603</v>
+      </c>
+      <c r="I1744" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1744" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1744" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1744" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1744" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1745" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1745" s="3"/>
-      <c r="C1745" s="4"/>
-      <c r="F1745" s="5"/>
-      <c r="G1745" s="5"/>
-      <c r="L1745" s="5"/>
-      <c r="M1745" s="6"/>
+      <c r="A1745" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="B1745" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1745" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1745" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1745" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1745" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1745" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1745" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I1745" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1745" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1745" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1745" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1745" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1746" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1746" s="3"/>
-      <c r="C1746" s="4"/>
-      <c r="F1746" s="5"/>
-      <c r="G1746" s="5"/>
-      <c r="L1746" s="5"/>
-      <c r="M1746" s="6"/>
+      <c r="A1746" s="6" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B1746" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1746" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1746" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1746" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1746" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1746" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1746" s="6" t="s">
+        <v>1605</v>
+      </c>
+      <c r="I1746" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1746" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1746" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1746" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1746" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1747" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1747" s="3"/>
-      <c r="C1747" s="4"/>
-      <c r="F1747" s="5"/>
-      <c r="G1747" s="5"/>
-      <c r="L1747" s="5"/>
-      <c r="M1747" s="6"/>
+      <c r="A1747" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B1747" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1747" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1747" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1747" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1747" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1747" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1747" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1747" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1747" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1747" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1747" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1747" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1748" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1748" s="3"/>
-      <c r="C1748" s="4"/>
-      <c r="F1748" s="5"/>
-      <c r="G1748" s="5"/>
-      <c r="L1748" s="5"/>
-      <c r="M1748" s="6"/>
+      <c r="A1748" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B1748" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1748" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1748" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1748" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1748" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1748" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1748" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1748" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1748" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1748" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1748" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1748" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1749" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1749" s="3"/>
-      <c r="C1749" s="4"/>
-      <c r="F1749" s="5"/>
-      <c r="G1749" s="5"/>
-      <c r="L1749" s="5"/>
-      <c r="M1749" s="6"/>
+      <c r="A1749" s="6" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B1749" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1749" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1749" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1749" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1749" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1749" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1749" s="6" t="s">
+        <v>1607</v>
+      </c>
+      <c r="I1749" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1749" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1749" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1749" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1749" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1750" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1750" s="3"/>
-      <c r="C1750" s="4"/>
-      <c r="F1750" s="5"/>
-      <c r="G1750" s="5"/>
-      <c r="L1750" s="5"/>
-      <c r="M1750" s="6"/>
+      <c r="A1750" s="6" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B1750" s="6" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C1750" s="8">
+        <v>18</v>
+      </c>
+      <c r="D1750" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1750" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1750" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1750" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1750" s="6" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I1750" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1750" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1750" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1750" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1750" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1751" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1751" s="3"/>
-      <c r="C1751" s="4"/>
-      <c r="F1751" s="5"/>
-      <c r="G1751" s="5"/>
-      <c r="L1751" s="5"/>
-      <c r="M1751" s="6"/>
+      <c r="A1751" s="6" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B1751" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1751" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1751" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1751" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1751" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1751" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1751" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1751" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1751" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1751" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1751" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1751" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1752" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1752" s="3"/>
-      <c r="C1752" s="4"/>
-      <c r="F1752" s="5"/>
-      <c r="G1752" s="5"/>
-      <c r="L1752" s="5"/>
-      <c r="M1752" s="6"/>
+      <c r="A1752" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="B1752" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1752" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1752" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1752" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1752" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1752" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1752" s="6" t="s">
+        <v>837</v>
+      </c>
+      <c r="I1752" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1752" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1752" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1752" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1752" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1753" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1753" s="3"/>
-      <c r="C1753" s="4"/>
-      <c r="F1753" s="5"/>
-      <c r="G1753" s="5"/>
-      <c r="L1753" s="5"/>
-      <c r="M1753" s="6"/>
+      <c r="A1753" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B1753" s="6" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C1753" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1753" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1753" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1753" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1753" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1753" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1753" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1753" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1753" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1753" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1753" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1754" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1754" s="3"/>
-      <c r="C1754" s="4"/>
-      <c r="F1754" s="5"/>
-      <c r="G1754" s="5"/>
-      <c r="L1754" s="5"/>
-      <c r="M1754" s="6"/>
+      <c r="A1754" s="6" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B1754" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1754" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1754" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1754" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1754" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1754" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1754" s="6" t="s">
+        <v>1431</v>
+      </c>
+      <c r="I1754" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1754" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1754" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1754" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1754" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1755" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1755" s="3"/>
-      <c r="C1755" s="4"/>
-      <c r="F1755" s="5"/>
-      <c r="G1755" s="5"/>
-      <c r="L1755" s="5"/>
-      <c r="M1755" s="6"/>
+      <c r="A1755" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1755" s="6" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C1755" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1755" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1755" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1755" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1755" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1755" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="I1755" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1755" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1755" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1755" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1755" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1756" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1756" s="3"/>
-      <c r="C1756" s="4"/>
-      <c r="F1756" s="5"/>
-      <c r="G1756" s="5"/>
-      <c r="L1756" s="5"/>
-      <c r="M1756" s="6"/>
+      <c r="A1756" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="B1756" s="6" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C1756" s="8">
+        <v>18</v>
+      </c>
+      <c r="D1756" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1756" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1756" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1756" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1756" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="I1756" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1756" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1756" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1756" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1756" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1757" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1757" s="3"/>
-      <c r="C1757" s="4"/>
-      <c r="F1757" s="5"/>
-      <c r="G1757" s="5"/>
-      <c r="L1757" s="5"/>
-      <c r="M1757" s="6"/>
+      <c r="A1757" s="6" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B1757" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1757" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1757" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1757" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1757" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1757" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1757" s="6" t="s">
+        <v>1609</v>
+      </c>
+      <c r="I1757" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1757" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1757" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1757" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1757" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1758" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1758" s="3"/>
-      <c r="C1758" s="4"/>
-      <c r="F1758" s="5"/>
-      <c r="G1758" s="5"/>
-      <c r="L1758" s="5"/>
-      <c r="M1758" s="6"/>
+      <c r="A1758" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1758" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1758" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1758" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1758" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1758" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1758" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1758" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1758" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1758" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1758" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1758" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1758" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1759" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1759" s="3"/>
-      <c r="C1759" s="4"/>
-      <c r="F1759" s="5"/>
-      <c r="G1759" s="5"/>
-      <c r="L1759" s="5"/>
-      <c r="M1759" s="6"/>
+      <c r="A1759" s="6" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B1759" s="6" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C1759" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1759" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1759" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1759" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1759" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1759" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1759" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1759" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1759" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1759" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1759" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1760" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1760" s="3"/>
-      <c r="C1760" s="4"/>
-      <c r="F1760" s="5"/>
-      <c r="G1760" s="5"/>
-      <c r="L1760" s="5"/>
-      <c r="M1760" s="6"/>
+      <c r="A1760" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1760" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1760" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1760" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1760" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1760" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1760" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1760" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1760" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1760" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1760" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1760" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1760" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1761" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1761" s="3"/>
-      <c r="C1761" s="4"/>
-      <c r="F1761" s="5"/>
-      <c r="G1761" s="5"/>
-      <c r="L1761" s="5"/>
-      <c r="M1761" s="6"/>
+      <c r="A1761" s="6" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B1761" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1761" s="8">
+        <v>40</v>
+      </c>
+      <c r="D1761" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1761" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1761" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1761" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1761" s="6" t="s">
+        <v>1612</v>
+      </c>
+      <c r="I1761" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1761" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1761" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1761" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1761" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1762" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1762" s="3"/>
-      <c r="C1762" s="4"/>
-      <c r="F1762" s="5"/>
-      <c r="G1762" s="5"/>
-      <c r="L1762" s="5"/>
-      <c r="M1762" s="6"/>
+      <c r="A1762" s="6" t="s">
+        <v>901</v>
+      </c>
+      <c r="B1762" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1762" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1762" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1762" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1762" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1762" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1762" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1762" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1762" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1762" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1762" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1762" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1763" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1763" s="3"/>
-      <c r="C1763" s="4"/>
-      <c r="F1763" s="5"/>
-      <c r="G1763" s="5"/>
-      <c r="L1763" s="5"/>
-      <c r="M1763" s="6"/>
+      <c r="A1763" s="6" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B1763" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1763" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1763" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1763" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1763" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1763" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1763" s="6" t="s">
+        <v>1614</v>
+      </c>
+      <c r="I1763" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1763" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1763" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1763" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1763" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1764" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1764" s="3"/>
-      <c r="C1764" s="4"/>
-      <c r="F1764" s="5"/>
-      <c r="G1764" s="5"/>
-      <c r="L1764" s="5"/>
-      <c r="M1764" s="6"/>
+      <c r="A1764" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1764" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1764" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1764" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1764" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1764" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1764" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1764" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I1764" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1764" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1764" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1764" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1764" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1765" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1765" s="3"/>
-      <c r="C1765" s="4"/>
-      <c r="F1765" s="5"/>
-      <c r="G1765" s="5"/>
-      <c r="L1765" s="5"/>
-      <c r="M1765" s="6"/>
+      <c r="A1765" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="B1765" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1765" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1765" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1765" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1765" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1765" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1765" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="I1765" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1765" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1765" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1765" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1765" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1766" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1766" s="3"/>
-      <c r="C1766" s="4"/>
-      <c r="F1766" s="5"/>
-      <c r="G1766" s="5"/>
-      <c r="L1766" s="5"/>
-      <c r="M1766" s="6"/>
+      <c r="A1766" s="6" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B1766" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1766" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1766" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1766" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1766" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1766" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1766" s="6" t="s">
+        <v>1616</v>
+      </c>
+      <c r="I1766" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1766" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1766" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1766" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1766" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1767" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1767" s="3"/>
-      <c r="C1767" s="4"/>
-      <c r="F1767" s="5"/>
-      <c r="G1767" s="5"/>
-      <c r="L1767" s="5"/>
-      <c r="M1767" s="6"/>
+      <c r="A1767" s="6" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B1767" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1767" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1767" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1767" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1767" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1767" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1767" s="6" t="s">
+        <v>1465</v>
+      </c>
+      <c r="I1767" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1767" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1767" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1767" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1767" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1768" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1768" s="3"/>
-      <c r="C1768" s="4"/>
-      <c r="F1768" s="5"/>
-      <c r="G1768" s="5"/>
-      <c r="L1768" s="5"/>
-      <c r="M1768" s="6"/>
+      <c r="A1768" s="6" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B1768" s="6" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C1768" s="8">
+        <v>20</v>
+      </c>
+      <c r="D1768" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1768" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1768" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1768" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1768" s="6" t="s">
+        <v>1619</v>
+      </c>
+      <c r="I1768" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1768" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1768" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1768" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1768" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1769" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1769" s="3"/>
-      <c r="C1769" s="4"/>
-      <c r="F1769" s="5"/>
-      <c r="G1769" s="5"/>
-      <c r="L1769" s="5"/>
-      <c r="M1769" s="6"/>
+      <c r="A1769" s="6" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B1769" s="6" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C1769" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1769" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1769" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1769" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1769" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1769" s="6" t="s">
+        <v>1431</v>
+      </c>
+      <c r="I1769" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1769" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1769" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1769" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1769" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1770" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1770" s="3"/>
-      <c r="C1770" s="4"/>
-      <c r="F1770" s="5"/>
-      <c r="G1770" s="5"/>
-      <c r="L1770" s="5"/>
-      <c r="M1770" s="6"/>
+      <c r="A1770" s="6" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B1770" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1770" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1770" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1770" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1770" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1770" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1770" s="6" t="s">
+        <v>1102</v>
+      </c>
+      <c r="I1770" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1770" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1770" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1770" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1770" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1771" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1771" s="3"/>
-      <c r="C1771" s="4"/>
-      <c r="F1771" s="5"/>
-      <c r="G1771" s="5"/>
-      <c r="L1771" s="5"/>
-      <c r="M1771" s="6"/>
+      <c r="A1771" s="6" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B1771" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1771" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1771" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1771" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1771" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1771" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1771" s="6" t="s">
+        <v>1621</v>
+      </c>
+      <c r="I1771" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1771" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1771" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1771" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1771" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1772" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1772" s="3"/>
-      <c r="C1772" s="4"/>
-      <c r="F1772" s="5"/>
-      <c r="G1772" s="5"/>
-      <c r="L1772" s="5"/>
-      <c r="M1772" s="6"/>
+      <c r="A1772" s="6" t="s">
+        <v>963</v>
+      </c>
+      <c r="B1772" s="6" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C1772" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1772" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1772" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1772" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1772" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1772" s="6" t="s">
+        <v>965</v>
+      </c>
+      <c r="I1772" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1772" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1772" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1772" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1772" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1773" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1773" s="3"/>
-      <c r="C1773" s="4"/>
-      <c r="F1773" s="5"/>
-      <c r="G1773" s="5"/>
-      <c r="L1773" s="5"/>
-      <c r="M1773" s="6"/>
+      <c r="A1773" s="6" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B1773" s="6" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C1773" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1773" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1773" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1773" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1773" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1773" s="6" t="s">
+        <v>1546</v>
+      </c>
+      <c r="I1773" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1773" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1773" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1773" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1773" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1774" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1774" s="3"/>
-      <c r="C1774" s="4"/>
-      <c r="F1774" s="5"/>
-      <c r="G1774" s="5"/>
-      <c r="L1774" s="5"/>
-      <c r="M1774" s="6"/>
+      <c r="A1774" s="6" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B1774" s="6" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C1774" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1774" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1774" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1774" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1774" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1774" s="6" t="s">
+        <v>1395</v>
+      </c>
+      <c r="I1774" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1774" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1774" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1774" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1774" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1775" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1775" s="3"/>
-      <c r="C1775" s="4"/>
-      <c r="F1775" s="5"/>
-      <c r="G1775" s="5"/>
-      <c r="L1775" s="5"/>
-      <c r="M1775" s="6"/>
+      <c r="A1775" s="6" t="s">
+        <v>821</v>
+      </c>
+      <c r="B1775" s="6" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C1775" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1775" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1775" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1775" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1775" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1775" s="6" t="s">
+        <v>822</v>
+      </c>
+      <c r="I1775" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1775" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1775" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1775" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1775" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1776" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1776" s="3"/>
-      <c r="C1776" s="4"/>
-      <c r="F1776" s="5"/>
-      <c r="G1776" s="5"/>
-      <c r="L1776" s="5"/>
-      <c r="M1776" s="6"/>
+      <c r="A1776" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B1776" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1776" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1776" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1776" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1776" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1776" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1776" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1776" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1776" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1776" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1776" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1776" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1777" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1777" s="3"/>
-      <c r="C1777" s="4"/>
-      <c r="F1777" s="5"/>
-      <c r="G1777" s="5"/>
-      <c r="L1777" s="5"/>
-      <c r="M1777" s="6"/>
+      <c r="A1777" s="6" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B1777" s="6" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C1777" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1777" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1777" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1777" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1777" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1777" s="6" t="s">
+        <v>1058</v>
+      </c>
+      <c r="I1777" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1777" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1777" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1777" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1777" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1778" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1778" s="3"/>
-      <c r="C1778" s="4"/>
-      <c r="F1778" s="5"/>
-      <c r="G1778" s="5"/>
-      <c r="L1778" s="5"/>
-      <c r="M1778" s="6"/>
+      <c r="A1778" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B1778" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1778" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1778" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1778" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1778" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1778" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1778" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1778" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1778" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1778" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1778" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1778" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1779" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1779" s="3"/>
-      <c r="C1779" s="4"/>
-      <c r="F1779" s="5"/>
-      <c r="G1779" s="5"/>
-      <c r="L1779" s="5"/>
-      <c r="M1779" s="6"/>
+      <c r="A1779" s="6" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B1779" s="6" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C1779" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1779" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1779" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1779" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1779" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1779" s="6" t="s">
+        <v>1623</v>
+      </c>
+      <c r="I1779" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1779" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1779" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1779" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1779" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1780" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1780" s="3"/>
-      <c r="C1780" s="4"/>
-      <c r="F1780" s="5"/>
-      <c r="G1780" s="5"/>
-      <c r="L1780" s="5"/>
-      <c r="M1780" s="6"/>
+      <c r="A1780" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="B1780" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1780" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1780" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1780" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1780" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1780" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1780" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="I1780" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1780" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1780" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1780" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1780" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1781" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1781" s="3"/>
-      <c r="C1781" s="4"/>
-      <c r="F1781" s="5"/>
-      <c r="G1781" s="5"/>
-      <c r="L1781" s="5"/>
-      <c r="M1781" s="6"/>
+      <c r="A1781" s="6" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B1781" s="6" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C1781" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1781" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1781" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1781" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1781" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1781" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1781" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1781" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1781" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1781" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1781" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1782" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1782" s="3"/>
-      <c r="C1782" s="4"/>
-      <c r="F1782" s="5"/>
-      <c r="G1782" s="5"/>
-      <c r="L1782" s="5"/>
-      <c r="M1782" s="6"/>
+      <c r="A1782" s="6" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B1782" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1782" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1782" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1782" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1782" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1782" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1782" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1782" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1782" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1782" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1782" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1782" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1783" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1783" s="3"/>
-      <c r="C1783" s="4"/>
-      <c r="F1783" s="5"/>
-      <c r="G1783" s="5"/>
-      <c r="L1783" s="5"/>
-      <c r="M1783" s="6"/>
+      <c r="A1783" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="B1783" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1783" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1783" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1783" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1783" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1783" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1783" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="I1783" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1783" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1783" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1783" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1783" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1784" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1784" s="3"/>
-      <c r="C1784" s="4"/>
-      <c r="F1784" s="5"/>
-      <c r="G1784" s="5"/>
-      <c r="L1784" s="5"/>
-      <c r="M1784" s="6"/>
+      <c r="A1784" s="6" t="s">
+        <v>901</v>
+      </c>
+      <c r="B1784" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1784" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1784" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1784" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1784" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1784" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1784" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1784" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1784" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1784" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1784" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1784" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1785" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1785" s="3"/>
-      <c r="C1785" s="4"/>
-      <c r="F1785" s="5"/>
-      <c r="G1785" s="5"/>
-      <c r="L1785" s="5"/>
-      <c r="M1785" s="6"/>
+      <c r="A1785" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1785" s="6" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C1785" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1785" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1785" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1785" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1785" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1785" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1785" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1785" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1785" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1785" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1785" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1786" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1786" s="3"/>
-      <c r="C1786" s="4"/>
-      <c r="F1786" s="5"/>
-      <c r="G1786" s="5"/>
-      <c r="L1786" s="5"/>
-      <c r="M1786" s="6"/>
+      <c r="A1786" s="6" t="s">
+        <v>856</v>
+      </c>
+      <c r="B1786" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1786" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1786" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1786" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1786" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1786" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1786" s="6" t="s">
+        <v>857</v>
+      </c>
+      <c r="I1786" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1786" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1786" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1786" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1786" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1787" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1787" s="3"/>
-      <c r="C1787" s="4"/>
-      <c r="F1787" s="5"/>
-      <c r="G1787" s="5"/>
-      <c r="L1787" s="5"/>
-      <c r="M1787" s="6"/>
+      <c r="A1787" s="6" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B1787" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1787" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1787" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1787" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="F1787" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1787" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1787" s="6" t="s">
+        <v>1625</v>
+      </c>
+      <c r="I1787" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1787" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1787" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1787" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1787" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1788" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1788" s="3"/>
-      <c r="C1788" s="4"/>
-      <c r="F1788" s="5"/>
-      <c r="G1788" s="5"/>
-      <c r="L1788" s="5"/>
-      <c r="M1788" s="6"/>
+      <c r="A1788" s="6" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B1788" s="6" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C1788" s="8">
+        <v>49</v>
+      </c>
+      <c r="D1788" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1788" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1788" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1788" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1788" s="6" t="s">
+        <v>1462</v>
+      </c>
+      <c r="I1788" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1788" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1788" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1788" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1788" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1789" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1789" s="3"/>
-      <c r="C1789" s="4"/>
-      <c r="F1789" s="5"/>
-      <c r="G1789" s="5"/>
-      <c r="L1789" s="5"/>
-      <c r="M1789" s="6"/>
+      <c r="A1789" s="6" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B1789" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1789" s="8">
+        <v>40</v>
+      </c>
+      <c r="D1789" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1789" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1789" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1789" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1789" s="6" t="s">
+        <v>1627</v>
+      </c>
+      <c r="I1789" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1789" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1789" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1789" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1789" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1790" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1790" s="3"/>
-      <c r="C1790" s="4"/>
-      <c r="F1790" s="5"/>
-      <c r="G1790" s="5"/>
-      <c r="L1790" s="5"/>
-      <c r="M1790" s="6"/>
+      <c r="A1790" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="B1790" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1790" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1790" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1790" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1790" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1790" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1790" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="I1790" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1790" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1790" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1790" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1790" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1791" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1791" s="3"/>
-      <c r="C1791" s="4"/>
-      <c r="F1791" s="5"/>
-      <c r="G1791" s="5"/>
-      <c r="L1791" s="5"/>
-      <c r="M1791" s="6"/>
+      <c r="A1791" s="6" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B1791" s="6" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C1791" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1791" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1791" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1791" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1791" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1791" s="6" t="s">
+        <v>1431</v>
+      </c>
+      <c r="I1791" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1791" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1791" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1791" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1791" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1792" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1792" s="3"/>
-      <c r="C1792" s="4"/>
-      <c r="F1792" s="5"/>
-      <c r="G1792" s="5"/>
-      <c r="L1792" s="5"/>
-      <c r="M1792" s="6"/>
+      <c r="A1792" s="6" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B1792" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1792" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1792" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1792" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1792" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1792" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1792" s="6" t="s">
+        <v>1629</v>
+      </c>
+      <c r="I1792" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1792" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1792" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1792" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1792" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1793" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1793" s="3"/>
-      <c r="C1793" s="4"/>
-      <c r="F1793" s="5"/>
-      <c r="G1793" s="5"/>
-      <c r="L1793" s="5"/>
-      <c r="M1793" s="6"/>
+      <c r="A1793" s="6" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B1793" s="6" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C1793" s="8">
+        <v>49</v>
+      </c>
+      <c r="D1793" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1793" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1793" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1793" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1793" s="6" t="s">
+        <v>1578</v>
+      </c>
+      <c r="I1793" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1793" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1793" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1793" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1793" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1794" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1794" s="3"/>
-      <c r="C1794" s="4"/>
-      <c r="F1794" s="5"/>
-      <c r="G1794" s="5"/>
-      <c r="L1794" s="5"/>
-      <c r="M1794" s="6"/>
+      <c r="A1794" s="6" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B1794" s="6" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C1794" s="8">
+        <v>18</v>
+      </c>
+      <c r="D1794" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1794" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1794" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1794" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1794" s="6" t="s">
+        <v>1631</v>
+      </c>
+      <c r="I1794" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1794" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1794" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1794" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1794" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1795" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1795" s="3"/>
-      <c r="C1795" s="4"/>
-      <c r="F1795" s="5"/>
-      <c r="G1795" s="5"/>
-      <c r="L1795" s="5"/>
-      <c r="M1795" s="6"/>
+      <c r="A1795" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="B1795" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1795" s="8">
+        <v>14</v>
+      </c>
+      <c r="D1795" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1795" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1795" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1795" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1795" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="I1795" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1795" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1795" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1795" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1795" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1796" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1796" s="3"/>
-      <c r="C1796" s="4"/>
-      <c r="F1796" s="5"/>
-      <c r="G1796" s="5"/>
-      <c r="L1796" s="5"/>
-      <c r="M1796" s="6"/>
+      <c r="A1796" s="6" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1796" s="6" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C1796" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1796" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1796" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1796" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1796" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1796" s="6" t="s">
+        <v>895</v>
+      </c>
+      <c r="I1796" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1796" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1796" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1796" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1796" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1797" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1797" s="3"/>
-      <c r="C1797" s="4"/>
-      <c r="F1797" s="5"/>
-      <c r="G1797" s="5"/>
-      <c r="L1797" s="5"/>
-      <c r="M1797" s="6"/>
+      <c r="A1797" s="6" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B1797" s="6" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C1797" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1797" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1797" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1797" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1797" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1797" s="6" t="s">
+        <v>1538</v>
+      </c>
+      <c r="I1797" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1797" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1797" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1797" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1797" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1798" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1798" s="3"/>
-      <c r="C1798" s="4"/>
-      <c r="F1798" s="5"/>
-      <c r="G1798" s="5"/>
-      <c r="L1798" s="5"/>
-      <c r="M1798" s="6"/>
+      <c r="A1798" s="6" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B1798" s="6" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C1798" s="8">
+        <v>18</v>
+      </c>
+      <c r="D1798" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1798" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1798" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1798" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1798" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1798" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1798" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1798" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1798" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1798" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1799" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1799" s="3"/>
-      <c r="C1799" s="4"/>
-      <c r="F1799" s="5"/>
-      <c r="G1799" s="5"/>
-      <c r="L1799" s="5"/>
-      <c r="M1799" s="6"/>
+      <c r="A1799" s="6" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B1799" s="6" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C1799" s="8">
+        <v>21</v>
+      </c>
+      <c r="D1799" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1799" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1799" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1799" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1799" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="I1799" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1799" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1799" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1799" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1799" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1800" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1800" s="3"/>
-      <c r="C1800" s="4"/>
-      <c r="F1800" s="5"/>
-      <c r="G1800" s="5"/>
-      <c r="L1800" s="5"/>
-      <c r="M1800" s="6"/>
+      <c r="A1800" s="6" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B1800" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1800" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1800" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1800" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1800" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1800" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1800" s="6" t="s">
+        <v>1337</v>
+      </c>
+      <c r="I1800" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1800" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1800" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1800" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1800" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1801" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1801" s="3"/>
-      <c r="C1801" s="4"/>
-      <c r="F1801" s="5"/>
-      <c r="G1801" s="5"/>
-      <c r="L1801" s="5"/>
-      <c r="M1801" s="6"/>
+      <c r="A1801" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B1801" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1801" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1801" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1801" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1801" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1801" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1801" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1801" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1801" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1801" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1801" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1801" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1802" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1802" s="3"/>
-      <c r="C1802" s="4"/>
-      <c r="F1802" s="5"/>
-      <c r="G1802" s="5"/>
-      <c r="L1802" s="5"/>
-      <c r="M1802" s="6"/>
+      <c r="A1802" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1802" s="6" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C1802" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1802" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1802" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1802" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1802" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1802" s="6" t="s">
+        <v>909</v>
+      </c>
+      <c r="I1802" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1802" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1802" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1802" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1802" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1803" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1803" s="3"/>
-      <c r="C1803" s="4"/>
-      <c r="F1803" s="5"/>
-      <c r="G1803" s="5"/>
-      <c r="L1803" s="5"/>
-      <c r="M1803" s="6"/>
+      <c r="A1803" s="6" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B1803" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1803" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1803" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1803" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1803" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1803" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1803" s="6" t="s">
+        <v>1634</v>
+      </c>
+      <c r="I1803" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1803" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1803" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1803" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1803" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1804" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1804" s="3"/>
-      <c r="C1804" s="4"/>
-      <c r="F1804" s="5"/>
-      <c r="G1804" s="5"/>
-      <c r="L1804" s="5"/>
-      <c r="M1804" s="6"/>
+      <c r="A1804" s="6" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B1804" s="6" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C1804" s="8">
+        <v>20</v>
+      </c>
+      <c r="D1804" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1804" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1804" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1804" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1804" s="6" t="s">
+        <v>1406</v>
+      </c>
+      <c r="I1804" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1804" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1804" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1804" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1804" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1805" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1805" s="3"/>
-      <c r="C1805" s="4"/>
-      <c r="F1805" s="5"/>
-      <c r="G1805" s="5"/>
-      <c r="L1805" s="5"/>
-      <c r="M1805" s="6"/>
+      <c r="A1805" s="6" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B1805" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1805" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1805" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1805" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1805" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1805" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1805" s="6" t="s">
+        <v>1637</v>
+      </c>
+      <c r="I1805" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1805" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1805" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1805" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1805" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1806" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1806" s="3"/>
-      <c r="C1806" s="4"/>
-      <c r="F1806" s="5"/>
-      <c r="G1806" s="5"/>
-      <c r="L1806" s="5"/>
-      <c r="M1806" s="6"/>
+      <c r="A1806" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="B1806" s="6" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1806" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1806" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1806" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1806" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1806" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1806" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="I1806" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1806" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1806" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1806" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1806" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1807" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1807" s="3"/>
-      <c r="C1807" s="4"/>
-      <c r="F1807" s="5"/>
-      <c r="G1807" s="5"/>
-      <c r="L1807" s="5"/>
-      <c r="M1807" s="6"/>
+      <c r="A1807" s="6" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B1807" s="6" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C1807" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1807" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1807" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1807" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1807" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1807" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1807" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1807" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1807" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1807" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1807" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1808" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1808" s="3"/>
-      <c r="C1808" s="4"/>
-      <c r="F1808" s="5"/>
-      <c r="G1808" s="5"/>
-      <c r="L1808" s="5"/>
-      <c r="M1808" s="6"/>
+      <c r="A1808" s="6" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B1808" s="6" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C1808" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1808" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1808" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1808" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1808" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1808" s="6" t="s">
+        <v>1640</v>
+      </c>
+      <c r="I1808" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1808" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1808" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1808" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1808" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1809" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1809" s="3"/>
-      <c r="C1809" s="4"/>
-      <c r="F1809" s="5"/>
-      <c r="G1809" s="5"/>
-      <c r="L1809" s="5"/>
-      <c r="M1809" s="6"/>
+      <c r="A1809" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B1809" s="6" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C1809" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1809" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1809" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="F1809" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1809" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1809" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="I1809" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1809" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1809" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1809" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1809" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1810" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1810" s="3"/>
-      <c r="C1810" s="4"/>
-      <c r="F1810" s="5"/>
-      <c r="G1810" s="5"/>
-      <c r="L1810" s="5"/>
-      <c r="M1810" s="6"/>
+      <c r="A1810" s="6" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B1810" s="6" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C1810" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1810" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1810" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1810" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1810" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1810" s="6" t="s">
+        <v>1102</v>
+      </c>
+      <c r="I1810" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1810" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1810" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1810" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1810" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1811" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1811" s="3"/>
-      <c r="C1811" s="4"/>
-      <c r="F1811" s="5"/>
-      <c r="G1811" s="5"/>
-      <c r="L1811" s="5"/>
-      <c r="M1811" s="6"/>
+      <c r="A1811" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B1811" s="6" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C1811" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1811" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1811" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1811" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1811" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1811" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1811" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1811" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1811" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1811" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1811" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1812" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1812" s="3"/>
-      <c r="C1812" s="4"/>
-      <c r="F1812" s="5"/>
-      <c r="G1812" s="5"/>
-      <c r="L1812" s="5"/>
-      <c r="M1812" s="6"/>
+      <c r="A1812" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B1812" s="6" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C1812" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1812" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1812" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1812" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1812" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1812" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1812" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1812" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1812" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1812" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1812" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1813" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1813" s="3"/>
-      <c r="C1813" s="4"/>
-      <c r="F1813" s="5"/>
-      <c r="G1813" s="5"/>
-      <c r="L1813" s="5"/>
-      <c r="M1813" s="6"/>
+      <c r="A1813" s="6" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B1813" s="6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1813" s="8">
+        <v>21</v>
+      </c>
+      <c r="D1813" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1813" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1813" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1813" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1813" s="6" t="s">
+        <v>1643</v>
+      </c>
+      <c r="I1813" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1813" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1813" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1813" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1813" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1814" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1814" s="3"/>
-      <c r="C1814" s="4"/>
-      <c r="F1814" s="5"/>
-      <c r="G1814" s="5"/>
-      <c r="L1814" s="5"/>
-      <c r="M1814" s="6"/>
+      <c r="A1814" s="6" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B1814" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1814" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1814" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1814" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1814" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1814" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1814" s="6" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I1814" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1814" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1814" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1814" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1814" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1815" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1815" s="3"/>
-      <c r="C1815" s="4"/>
-      <c r="F1815" s="5"/>
-      <c r="G1815" s="5"/>
-      <c r="L1815" s="5"/>
-      <c r="M1815" s="6"/>
+      <c r="A1815" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B1815" s="6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1815" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1815" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1815" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1815" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1815" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1815" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1815" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1815" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1815" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1815" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1815" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1816" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1816" s="3"/>
-      <c r="C1816" s="4"/>
-      <c r="F1816" s="5"/>
-      <c r="G1816" s="5"/>
-      <c r="L1816" s="5"/>
-      <c r="M1816" s="6"/>
+      <c r="A1816" s="6" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B1816" s="6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1816" s="8">
+        <v>21</v>
+      </c>
+      <c r="D1816" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1816" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1816" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1816" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1816" s="6" t="s">
+        <v>1646</v>
+      </c>
+      <c r="I1816" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1816" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1816" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1816" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1816" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1817" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1817" s="3"/>
-      <c r="C1817" s="4"/>
-      <c r="F1817" s="5"/>
-      <c r="G1817" s="5"/>
-      <c r="L1817" s="5"/>
-      <c r="M1817" s="6"/>
+      <c r="A1817" s="6" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B1817" s="6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1817" s="8">
+        <v>21</v>
+      </c>
+      <c r="D1817" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1817" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1817" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1817" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1817" s="6" t="s">
+        <v>1648</v>
+      </c>
+      <c r="I1817" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1817" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1817" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1817" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1817" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1818" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1818" s="3"/>
-      <c r="C1818" s="4"/>
-      <c r="F1818" s="5"/>
-      <c r="G1818" s="5"/>
-      <c r="L1818" s="5"/>
-      <c r="M1818" s="6"/>
+      <c r="A1818" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1818" s="6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1818" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1818" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1818" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1818" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1818" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1818" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I1818" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1818" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1818" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1818" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1818" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1819" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1819" s="3"/>
-      <c r="C1819" s="4"/>
-      <c r="F1819" s="5"/>
-      <c r="G1819" s="5"/>
-      <c r="L1819" s="5"/>
-      <c r="M1819" s="6"/>
+      <c r="A1819" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B1819" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1819" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1819" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1819" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1819" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1819" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1819" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1819" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1819" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1819" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1819" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1819" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1820" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1820" s="3"/>
-      <c r="C1820" s="4"/>
-      <c r="F1820" s="5"/>
-      <c r="G1820" s="5"/>
-      <c r="L1820" s="5"/>
-      <c r="M1820" s="6"/>
+      <c r="A1820" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="B1820" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1820" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1820" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1820" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1820" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1820" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1820" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1820" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1820" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1820" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1820" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1820" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1821" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1821" s="3"/>
-      <c r="C1821" s="4"/>
-      <c r="F1821" s="5"/>
-      <c r="G1821" s="5"/>
-      <c r="L1821" s="5"/>
-      <c r="M1821" s="6"/>
+      <c r="A1821" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="B1821" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1821" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1821" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1821" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="F1821" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1821" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1821" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="I1821" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1821" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1821" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1821" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1821" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1822" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1822" s="3"/>
-      <c r="C1822" s="4"/>
-      <c r="F1822" s="5"/>
-      <c r="G1822" s="5"/>
-      <c r="L1822" s="5"/>
-      <c r="M1822" s="6"/>
+      <c r="A1822" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="B1822" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1822" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1822" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1822" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1822" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1822" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1822" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="I1822" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1822" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1822" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1822" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1822" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1823" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1823" s="3"/>
-      <c r="C1823" s="4"/>
-      <c r="F1823" s="5"/>
-      <c r="G1823" s="5"/>
-      <c r="L1823" s="5"/>
-      <c r="M1823" s="6"/>
+      <c r="A1823" s="6" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B1823" s="6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1823" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1823" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1823" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1823" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1823" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1823" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1823" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1823" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1823" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1823" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1823" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1824" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1824" s="3"/>
-      <c r="C1824" s="4"/>
-      <c r="F1824" s="5"/>
-      <c r="G1824" s="5"/>
-      <c r="L1824" s="5"/>
-      <c r="M1824" s="6"/>
+      <c r="A1824" s="6" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B1824" s="6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1824" s="8">
+        <v>21</v>
+      </c>
+      <c r="D1824" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1824" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1824" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1824" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1824" s="6" t="s">
+        <v>1578</v>
+      </c>
+      <c r="I1824" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1824" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1824" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1824" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1824" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1825" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1825" s="3"/>
-      <c r="C1825" s="4"/>
-      <c r="F1825" s="5"/>
-      <c r="G1825" s="5"/>
-      <c r="L1825" s="5"/>
-      <c r="M1825" s="6"/>
+      <c r="A1825" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="B1825" s="6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1825" s="8">
+        <v>21</v>
+      </c>
+      <c r="D1825" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1825" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1825" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1825" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1825" s="6" t="s">
+        <v>908</v>
+      </c>
+      <c r="I1825" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1825" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1825" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1825" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1825" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1826" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1826" s="3"/>
-      <c r="C1826" s="4"/>
-      <c r="F1826" s="5"/>
-      <c r="G1826" s="5"/>
-      <c r="L1826" s="5"/>
-      <c r="M1826" s="6"/>
+      <c r="A1826" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1826" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1826" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1826" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1826" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1826" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1826" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1826" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1826" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1826" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1826" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1826" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1826" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1827" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1827" s="3"/>
-      <c r="C1827" s="4"/>
-      <c r="F1827" s="5"/>
-      <c r="G1827" s="5"/>
-      <c r="L1827" s="5"/>
-      <c r="M1827" s="6"/>
+      <c r="A1827" s="6" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B1827" s="6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1827" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1827" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1827" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1827" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1827" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1827" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1827" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1827" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1827" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1827" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1827" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1828" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1828" s="3"/>
-      <c r="C1828" s="4"/>
-      <c r="F1828" s="5"/>
-      <c r="G1828" s="5"/>
-      <c r="L1828" s="5"/>
-      <c r="M1828" s="6"/>
+      <c r="A1828" s="6" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B1828" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1828" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1828" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1828" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1828" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1828" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1828" s="6" t="s">
+        <v>1605</v>
+      </c>
+      <c r="I1828" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1828" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1828" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1828" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1828" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1829" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1829" s="3"/>
-      <c r="C1829" s="4"/>
-      <c r="F1829" s="5"/>
-      <c r="G1829" s="5"/>
-      <c r="L1829" s="5"/>
-      <c r="M1829" s="6"/>
+      <c r="A1829" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B1829" s="6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1829" s="8">
+        <v>21</v>
+      </c>
+      <c r="D1829" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1829" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1829" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1829" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1829" s="6" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1829" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1829" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1829" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1829" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1829" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1830" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1830" s="3"/>
-      <c r="C1830" s="4"/>
-      <c r="F1830" s="5"/>
-      <c r="G1830" s="5"/>
-      <c r="L1830" s="5"/>
-      <c r="M1830" s="6"/>
+      <c r="A1830" s="6" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B1830" s="6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1830" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1830" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1830" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1830" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1830" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1830" s="6" t="s">
+        <v>1650</v>
+      </c>
+      <c r="I1830" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1830" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1830" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1830" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1830" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1831" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1831" s="3"/>
-      <c r="C1831" s="4"/>
-      <c r="F1831" s="5"/>
-      <c r="G1831" s="5"/>
-      <c r="L1831" s="5"/>
-      <c r="M1831" s="6"/>
+      <c r="A1831" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1831" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1831" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1831" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1831" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1831" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1831" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1831" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I1831" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1831" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1831" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1831" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1831" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1832" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1832" s="3"/>
-      <c r="C1832" s="4"/>
-      <c r="F1832" s="5"/>
-      <c r="G1832" s="5"/>
-      <c r="L1832" s="5"/>
-      <c r="M1832" s="6"/>
+      <c r="A1832" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="B1832" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1832" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1832" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1832" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1832" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1832" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1832" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="I1832" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1832" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1832" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1832" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1832" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1833" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1833" s="3"/>
-      <c r="C1833" s="4"/>
-      <c r="F1833" s="5"/>
-      <c r="G1833" s="5"/>
-      <c r="L1833" s="5"/>
-      <c r="M1833" s="6"/>
+      <c r="A1833" s="6" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B1833" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1833" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1833" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1833" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1833" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1833" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1833" s="6" t="s">
+        <v>1652</v>
+      </c>
+      <c r="I1833" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1833" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1833" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1833" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1833" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1834" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1834" s="3"/>
-      <c r="C1834" s="4"/>
-      <c r="F1834" s="5"/>
-      <c r="G1834" s="5"/>
-      <c r="L1834" s="5"/>
-      <c r="M1834" s="6"/>
+      <c r="A1834" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1834" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1834" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1834" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1834" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1834" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1834" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1834" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="I1834" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1834" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1834" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1834" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1834" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1835" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1835" s="3"/>
-      <c r="C1835" s="4"/>
-      <c r="F1835" s="5"/>
-      <c r="G1835" s="5"/>
-      <c r="L1835" s="5"/>
-      <c r="M1835" s="6"/>
+      <c r="A1835" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B1835" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1835" s="8">
+        <v>42</v>
+      </c>
+      <c r="D1835" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1835" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1835" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1835" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1835" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1835" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1835" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1835" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1835" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1835" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1836" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1836" s="3"/>
-      <c r="C1836" s="4"/>
-      <c r="F1836" s="5"/>
-      <c r="G1836" s="5"/>
-      <c r="L1836" s="5"/>
-      <c r="M1836" s="6"/>
+      <c r="A1836" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="B1836" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1836" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1836" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1836" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1836" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1836" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1836" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="I1836" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1836" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1836" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1836" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1836" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1837" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1837" s="3"/>
-      <c r="C1837" s="4"/>
-      <c r="F1837" s="5"/>
-      <c r="G1837" s="5"/>
-      <c r="L1837" s="5"/>
-      <c r="M1837" s="6"/>
+      <c r="A1837" s="6" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B1837" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1837" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1837" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1837" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1837" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1837" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1837" s="6" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I1837" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1837" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1837" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1837" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1837" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1838" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1838" s="3"/>
-      <c r="C1838" s="4"/>
-      <c r="F1838" s="5"/>
-      <c r="G1838" s="5"/>
-      <c r="L1838" s="5"/>
-      <c r="M1838" s="6"/>
+      <c r="A1838" s="6" t="s">
+        <v>970</v>
+      </c>
+      <c r="B1838" s="6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1838" s="8">
+        <v>21</v>
+      </c>
+      <c r="D1838" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1838" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1838" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1838" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1838" s="6" t="s">
+        <v>971</v>
+      </c>
+      <c r="I1838" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1838" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1838" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1838" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1838" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1839" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1839" s="3"/>
-      <c r="C1839" s="4"/>
-      <c r="F1839" s="5"/>
-      <c r="G1839" s="5"/>
-      <c r="L1839" s="5"/>
-      <c r="M1839" s="6"/>
+      <c r="A1839" s="6" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B1839" s="6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1839" s="8">
+        <v>56</v>
+      </c>
+      <c r="D1839" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1839" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1839" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1839" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1839" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1839" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1839" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1839" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1839" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1839" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1840" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1840" s="3"/>
-      <c r="C1840" s="4"/>
-      <c r="F1840" s="5"/>
-      <c r="G1840" s="5"/>
-      <c r="L1840" s="5"/>
-      <c r="M1840" s="6"/>
+      <c r="A1840" s="6" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B1840" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1840" s="8">
+        <v>12</v>
+      </c>
+      <c r="D1840" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1840" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1840" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1840" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1840" s="6" t="s">
+        <v>1395</v>
+      </c>
+      <c r="I1840" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1840" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1840" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1840" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1840" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1841" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1841" s="3"/>
-      <c r="C1841" s="4"/>
-      <c r="F1841" s="5"/>
-      <c r="G1841" s="5"/>
-      <c r="L1841" s="5"/>
-      <c r="M1841" s="6"/>
+      <c r="A1841" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="B1841" s="6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1841" s="8">
+        <v>21</v>
+      </c>
+      <c r="D1841" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1841" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1841" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1841" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1841" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="I1841" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1841" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1841" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1841" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1841" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="1842" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1842" s="3"/>
@@ -84316,17 +89404,12 @@
       <c r="M2900" s="6"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C1695:C2900">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C699">
+  <conditionalFormatting sqref="C2:C1694 C1842:C2900">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C700:C1694">
+  <conditionalFormatting sqref="C1695:C1841">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
